--- a/Java基礎①_変数_演習問題.xlsx
+++ b/Java基礎①_変数_演習問題.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\pleiades-2024-12-java-win-64bit-jre_20250120\workspace\Java\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0C802152-D4BA-4B39-AFBF-3691680852F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AC169BD-08C7-4F8B-B523-345BD249719E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="1" xr2:uid="{D2EB637F-B022-47FB-AE76-97F394918620}"/>
+    <workbookView xWindow="32220" yWindow="1395" windowWidth="17280" windowHeight="12390" firstSheet="1" activeTab="1" xr2:uid="{D2EB637F-B022-47FB-AE76-97F394918620}"/>
   </bookViews>
   <sheets>
     <sheet name="第1章 Javaプログラミングの基礎" sheetId="2" r:id="rId1"/>
@@ -306,9 +306,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>自分の名前、年齢、誕生日を入力し、それらの情報を特定のフォーマットでコンソールに出力してください。</t>
-  </si>
-  <si>
     <t>例えば「名前: エイフォース 太郎, 年齢: 30歳, 誕生日: 1995-05-15」のように表示します。</t>
   </si>
   <si>
@@ -320,9 +317,6 @@
       <t>トイ</t>
     </rPh>
     <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>問題: 商品の名前、価格、購入個数を入力し、複数購入した場合の合計金額をコンソールに出力してください。</t>
   </si>
   <si>
     <t>例えば、次の通り出力します。</t>
@@ -621,6 +615,14 @@
   </si>
   <si>
     <t>次の3つのデータ型を使って変数を宣言し、それぞれの値を表示するプログラムを作成してください。</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>自分の名前、年齢、誕生日を入力し、それらの情報を特定のフォーマットでコンソールに出力してください。</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>問題: 商品の名前、価格、購入個数を入力し、複数購入した場合の合計金額をコンソールに出力してください。</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -1059,7 +1061,7 @@
         <v>3</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.45">
@@ -1067,7 +1069,7 @@
         <v>4</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.45">
@@ -1075,7 +1077,7 @@
         <v>5</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.45">
@@ -1083,12 +1085,12 @@
         <v>6</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.45">
       <c r="C10" s="2" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.45">
@@ -1101,7 +1103,7 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.45">
       <c r="C13" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.45">
@@ -1137,10 +1139,10 @@
         <v>15</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.45">
@@ -1173,7 +1175,7 @@
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.45">
       <c r="C29" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.45">
@@ -1261,7 +1263,7 @@
         <v>37</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="55" spans="2:8" x14ac:dyDescent="0.45">
@@ -1269,7 +1271,7 @@
         <v>38</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="57" spans="2:8" x14ac:dyDescent="0.45">
@@ -1279,7 +1281,7 @@
     </row>
     <row r="58" spans="2:8" x14ac:dyDescent="0.45">
       <c r="C58" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
   </sheetData>
@@ -1386,12 +1388,12 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B19" s="2" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B20" s="2" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.45">
@@ -1432,48 +1434,48 @@
         <v>61</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>62</v>
+        <v>122</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B30" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B31" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A33" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>66</v>
+        <v>123</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B34" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B35" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A37" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B38" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.45">
@@ -1483,27 +1485,27 @@
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B40" s="2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B41" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B42" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B43" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B44" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.45">
@@ -1518,15 +1520,15 @@
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A48" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B49" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.45">
@@ -1536,22 +1538,22 @@
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B51" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B52" s="2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B53" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B54" s="2" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.45">
@@ -1566,142 +1568,142 @@
     </row>
     <row r="58" spans="1:2" ht="15.6" x14ac:dyDescent="0.45">
       <c r="A58" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B59" s="2" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B60" s="2" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B61" s="2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B62" s="2" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A64" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B65" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B66" s="2" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B67" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B68" s="2" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A70" s="2" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B71" s="2" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B72" s="2" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B73" s="2" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B75" s="2" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B76" s="2" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B77" s="2" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A79" s="2" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B80" s="2" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B81" s="2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B82" s="2" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A84" s="2" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B85" s="2" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B86" s="2" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B87" s="2" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
   </sheetData>
@@ -1711,6 +1713,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="4f770298-b31c-4238-a90d-db1340869ae4">
@@ -1719,15 +1730,6 @@
     <TaxCatchAll xmlns="4ebca473-6c88-4eeb-9b46-7f2093239612" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1938,20 +1940,20 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{68EEC494-2A78-4B3D-9A2E-CC561A7B8B93}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{61D35B6F-58DC-4BFD-8311-2E7BC05345C9}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="4f770298-b31c-4238-a90d-db1340869ae4"/>
     <ds:schemaRef ds:uri="4ebca473-6c88-4eeb-9b46-7f2093239612"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{68EEC494-2A78-4B3D-9A2E-CC561A7B8B93}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/Java基礎①_変数_演習問題.xlsx
+++ b/Java基礎①_変数_演習問題.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\pleiades-2024-12-java-win-64bit-jre_20250120\workspace\Java\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AC169BD-08C7-4F8B-B523-345BD249719E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80FE7ABE-86E3-45BC-9F67-7D8E162A62A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="32220" yWindow="1395" windowWidth="17280" windowHeight="12390" firstSheet="1" activeTab="1" xr2:uid="{D2EB637F-B022-47FB-AE76-97F394918620}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" firstSheet="1" activeTab="1" xr2:uid="{D2EB637F-B022-47FB-AE76-97F394918620}"/>
   </bookViews>
   <sheets>
     <sheet name="第1章 Javaプログラミングの基礎" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="128">
   <si>
     <t>第1章：Javaプログラミングの基礎</t>
     <phoneticPr fontId="2"/>
@@ -625,12 +625,40 @@
     <t>問題: 商品の名前、価格、購入個数を入力し、複数購入した場合の合計金額をコンソールに出力してください。</t>
     <phoneticPr fontId="2"/>
   </si>
+  <si>
+    <t>c</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>B,D</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>○</t>
+  </si>
+  <si>
+    <r>
+      <t>メソッドの中で宣言された変数は、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>使う前に必ず値を代入しなければならないから</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -667,6 +695,14 @@
       <name val="Microsoft YaHei"/>
       <family val="3"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1292,7 +1328,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6F23503-494B-4FE6-85E2-0289A1187C5D}">
-  <dimension ref="A1:B87"/>
+  <dimension ref="A1:G87"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="5.19921875" style="2" customWidth="1"/>
@@ -1447,7 +1483,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A33" s="2" t="s">
         <v>64</v>
       </c>
@@ -1455,17 +1491,17 @@
         <v>123</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.45">
       <c r="B34" s="2" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.45">
       <c r="B35" s="2" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A37" s="2" t="s">
         <v>67</v>
       </c>
@@ -1473,52 +1509,55 @@
         <v>68</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.45">
       <c r="B38" s="2" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.45">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.45">
       <c r="B39" s="2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.45">
       <c r="B40" s="2" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.45">
       <c r="B41" s="2" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.45">
       <c r="B42" s="2" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.45">
       <c r="B43" s="2" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.45">
       <c r="B44" s="2" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="G44" s="2">
+        <v>-45</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.45">
       <c r="B45" s="2" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.45">
       <c r="B46" s="2" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A48" s="2" t="s">
         <v>75</v>
       </c>
@@ -1526,47 +1565,50 @@
         <v>68</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.45">
       <c r="B49" s="2" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.45">
       <c r="B50" s="2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.45">
       <c r="B51" s="2" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.45">
       <c r="B52" s="2" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.45">
       <c r="B53" s="2" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.45">
       <c r="B54" s="2" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.45">
       <c r="B55" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="G55" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.45">
       <c r="B56" s="2" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="58" spans="1:2" ht="15.6" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:7" ht="15.6" x14ac:dyDescent="0.45">
       <c r="A58" s="2" t="s">
         <v>80</v>
       </c>
@@ -1574,27 +1616,30 @@
         <v>81</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.45">
       <c r="B59" s="2" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.45">
       <c r="B60" s="2" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.45">
       <c r="B61" s="2" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.45">
       <c r="B62" s="2" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="G62" s="2" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A64" s="2" t="s">
         <v>86</v>
       </c>
@@ -1602,27 +1647,30 @@
         <v>87</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.45">
       <c r="B65" s="2" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.45">
       <c r="B66" s="2" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:7" x14ac:dyDescent="0.45">
       <c r="B67" s="2" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="68" spans="1:7" x14ac:dyDescent="0.45">
       <c r="B68" s="2" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="G68" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A70" s="2" t="s">
         <v>92</v>
       </c>
@@ -1630,37 +1678,40 @@
         <v>93</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="71" spans="1:7" x14ac:dyDescent="0.45">
       <c r="B71" s="2" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="72" spans="1:7" x14ac:dyDescent="0.45">
       <c r="B72" s="2" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="73" spans="1:7" x14ac:dyDescent="0.45">
       <c r="B73" s="2" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="75" spans="1:7" x14ac:dyDescent="0.45">
       <c r="B75" s="2" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="76" spans="1:7" x14ac:dyDescent="0.45">
       <c r="B76" s="2" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="77" spans="1:7" x14ac:dyDescent="0.45">
       <c r="B77" s="2" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="G77" s="2" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A79" s="2" t="s">
         <v>100</v>
       </c>
@@ -1668,22 +1719,25 @@
         <v>87</v>
       </c>
     </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="80" spans="1:7" x14ac:dyDescent="0.45">
       <c r="B80" s="2" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.45">
       <c r="B81" s="2" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.45">
       <c r="B82" s="2" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="F82" s="2">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A84" s="2" t="s">
         <v>104</v>
       </c>
@@ -1691,19 +1745,25 @@
         <v>105</v>
       </c>
     </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.45">
       <c r="B85" s="2" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.45">
       <c r="B86" s="2" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="F86" s="2" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" ht="18" x14ac:dyDescent="0.45">
       <c r="B87" s="2" t="s">
         <v>91</v>
+      </c>
+      <c r="F87" t="s">
+        <v>127</v>
       </c>
     </row>
   </sheetData>
@@ -1713,15 +1773,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="4f770298-b31c-4238-a90d-db1340869ae4">
@@ -1730,6 +1781,15 @@
     <TaxCatchAll xmlns="4ebca473-6c88-4eeb-9b46-7f2093239612" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1940,20 +2000,20 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{68EEC494-2A78-4B3D-9A2E-CC561A7B8B93}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{61D35B6F-58DC-4BFD-8311-2E7BC05345C9}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="4f770298-b31c-4238-a90d-db1340869ae4"/>
     <ds:schemaRef ds:uri="4ebca473-6c88-4eeb-9b46-7f2093239612"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{68EEC494-2A78-4B3D-9A2E-CC561A7B8B93}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
